--- a/template/huawei_configuration.xlsx
+++ b/template/huawei_configuration.xlsx
@@ -28989,7 +28989,11 @@
           <t>Base Station Name</t>
         </is>
       </c>
-      <c r="C1" s="5" t="n"/>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Cell ID + Base Station Name</t>
+        </is>
+      </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Cell ID</t>
